--- a/resources/LaraYaiza_tabel_STX.xlsx
+++ b/resources/LaraYaiza_tabel_STX.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rubid\Documents\1_Prio_Biomedizin\AAA\00_AAA_BIO253\Bio253_SA6850_Research_in_Omics_HS2025-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rubid\Desktop\Bio253_SA6850_Research_in_Omics_HS2025\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856E7D82-EFE0-47C6-AA9A-9731B3C26248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE596C04-CD49-47D7-8962-773D90EA155C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13276" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,11 @@
     <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="46">
   <si>
     <t>Data: Scaffold</t>
   </si>
@@ -157,6 +156,9 @@
   </si>
   <si>
     <t>CLEAN DATA ON SHEET 2</t>
+  </si>
+  <si>
+    <t>log2-FC</t>
   </si>
 </sst>
 </file>
@@ -468,6 +470,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -486,7 +489,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -779,7 +781,7 @@
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="22" t="s">
         <v>44</v>
       </c>
       <c r="I3" s="1"/>
@@ -28938,7 +28940,9 @@
       <c r="V1" s="1"/>
     </row>
     <row r="2" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -28966,24 +28970,24 @@
       <c r="B3" s="10"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="22" t="s">
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="K3" s="23"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="25" t="s">
+      <c r="K3" s="24"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="28"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
       <c r="S3" s="10"/>

--- a/resources/LaraYaiza_tabel_STX.xlsx
+++ b/resources/LaraYaiza_tabel_STX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rubid\Desktop\Bio253_SA6850_Research_in_Omics_HS2025\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE596C04-CD49-47D7-8962-773D90EA155C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90775F5A-F8D2-44EB-A6BA-66E6242F7D92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13276" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
